--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/06_Müşteri ve Sözleşme Yönetimi/EKG-SAT-FRM-05_musteri_memnuniyet_anketi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/06_Müşteri ve Sözleşme Yönetimi/EKG-SAT-FRM-05_musteri_memnuniyet_anketi.xlsx
@@ -773,7 +773,8 @@
   <pageSetup paperSize="9" scale="73" orientation="portrait" r:id="rId1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-SAT-FRM-05&amp;C&amp;"Arial,Regular"&amp;11Müşteri Memnuniyet Anketi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Ankette müşteri, dönem ve uygulanmaz cevabı tanımlandı; bireysel puan ile NPS ayrıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
